--- a/A/chrV:192291-240363_41_finemapping.xlsx
+++ b/A/chrV:192291-240363_41_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="2845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2837" uniqueCount="2837">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">14/25</t>
   </si>
   <si>
-    <t xml:space="preserve">314/1971</t>
+    <t xml:space="preserve">322/1971</t>
   </si>
   <si>
     <t xml:space="preserve">YCR004C/YDR032C/YGL234W/YGR254W/YGR256W/YHR174W/YHR216W/YKL035W/YKR058W/YMR105C/YMR250W/YOR184W/YPL028W/YPR160W</t>
@@ -7514,19 +7514,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -7908,21 +7899,6 @@
   </si>
   <si>
     <t xml:space="preserve">PHO5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -8985,48 +8961,42 @@
         <v>2496</v>
       </c>
       <c r="Z1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" t="s">
         <v>2497</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>2498</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>2499</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>2500</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>2501</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>2502</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>2503</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>2504</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>2505</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>2506</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -9080,59 +9050,57 @@
         <v>196983</v>
       </c>
       <c r="U2" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="V2" t="n">
         <v>720813</v>
       </c>
       <c r="W2" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-0.132817152463257</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0249820927945862</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>2509</v>
       </c>
       <c r="AD2" t="s">
         <v>19</v>
       </c>
       <c r="AE2" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AH2" t="n">
+        <v>2509</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" t="b">
+      <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>2508</v>
+      <c r="AH2" t="s">
+        <v>2505</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>2513</v>
+        <v>2510</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -9186,62 +9154,60 @@
         <v>196983</v>
       </c>
       <c r="U3" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="V3" t="n">
         <v>231281</v>
       </c>
       <c r="W3" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.242703285976317</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0511593154656801</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>2512</v>
       </c>
       <c r="AD3" t="s">
         <v>19</v>
       </c>
       <c r="AE3" t="s">
-        <v>2515</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>2515</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>2512</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" t="b">
+      <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>2516</v>
+      <c r="AH3" t="s">
+        <v>2513</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="D4" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="E4" t="n">
         <v>191306</v>
@@ -9292,62 +9258,60 @@
         <v>198538</v>
       </c>
       <c r="U4" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="V4" t="n">
         <v>451327</v>
       </c>
       <c r="W4" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0.0520388350742155</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.0115509882741247</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>2517</v>
       </c>
       <c r="AD4" t="s">
         <v>19</v>
       </c>
       <c r="AE4" t="s">
-        <v>2520</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>2520</v>
-      </c>
-      <c r="AH4" t="n">
+        <v>2517</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="AI4" t="b">
+      <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>2521</v>
+      <c r="AH4" t="s">
+        <v>2518</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>2522</v>
+        <v>2519</v>
       </c>
       <c r="D5" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="E5" t="n">
         <v>191306</v>
@@ -9398,59 +9362,57 @@
         <v>196554</v>
       </c>
       <c r="U5" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="V5" t="n">
         <v>1154075</v>
       </c>
       <c r="W5" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.321381303194576</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0755024669997342</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>2509</v>
       </c>
       <c r="AD5" t="s">
         <v>19</v>
       </c>
       <c r="AE5" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AH5" t="n">
+        <v>2509</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" t="b">
+      <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>2524</v>
+      <c r="AH5" t="s">
+        <v>2521</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>2525</v>
+        <v>2522</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -9504,59 +9466,57 @@
         <v>196983</v>
       </c>
       <c r="U6" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="V6" t="n">
         <v>503947</v>
       </c>
       <c r="W6" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.081618863457653</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.0212691074979982</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>2509</v>
       </c>
       <c r="AD6" t="s">
         <v>19</v>
       </c>
       <c r="AE6" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AH6" t="n">
+        <v>2509</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" t="b">
+      <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>2526</v>
+      <c r="AH6" t="s">
+        <v>2523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>2527</v>
+        <v>2524</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -9610,62 +9570,60 @@
         <v>196983</v>
       </c>
       <c r="U7" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="V7" t="n">
         <v>550464</v>
       </c>
       <c r="W7" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-0.115666392984832</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0307263169980248</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>2526</v>
       </c>
       <c r="AD7" t="s">
         <v>19</v>
       </c>
       <c r="AE7" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AH7" t="n">
+        <v>2526</v>
+      </c>
+      <c r="AF7" t="n">
         <v>0</v>
       </c>
-      <c r="AI7" t="b">
+      <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>2530</v>
+      <c r="AH7" t="s">
+        <v>2527</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>2531</v>
+        <v>2528</v>
       </c>
       <c r="D8" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="E8" t="n">
         <v>195746</v>
@@ -9716,59 +9674,57 @@
         <v>196554</v>
       </c>
       <c r="U8" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="V8" t="n">
         <v>95445</v>
       </c>
       <c r="W8" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.0840435262215032</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.023241352970811</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>2530</v>
       </c>
       <c r="AD8" t="s">
         <v>19</v>
       </c>
       <c r="AE8" t="s">
-        <v>2533</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>2533</v>
-      </c>
-      <c r="AH8" t="n">
+        <v>2530</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" t="b">
+      <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>2534</v>
+      <c r="AH8" t="s">
+        <v>2531</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -9822,62 +9778,60 @@
         <v>196983</v>
       </c>
       <c r="U9" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="V9" t="n">
         <v>829918</v>
       </c>
       <c r="W9" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.106368285845023</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0300317637971942</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>2526</v>
       </c>
       <c r="AD9" t="s">
         <v>19</v>
       </c>
       <c r="AE9" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AH9" t="n">
+        <v>2526</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" t="b">
+      <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>2536</v>
+      <c r="AH9" t="s">
+        <v>2533</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="D10" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="E10" t="n">
         <v>183957</v>
@@ -9928,62 +9882,60 @@
         <v>198538</v>
       </c>
       <c r="U10" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="V10" t="n">
         <v>649266</v>
       </c>
       <c r="W10" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-0.0868418186300375</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.0247117960074415</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>2536</v>
       </c>
       <c r="AD10" t="s">
         <v>19</v>
       </c>
       <c r="AE10" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AH10" t="n">
+        <v>2536</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" t="b">
+      <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>2540</v>
+      <c r="AH10" t="s">
+        <v>2537</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
       <c r="D11" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="E11" t="n">
         <v>195746</v>
@@ -10034,62 +9986,60 @@
         <v>198538</v>
       </c>
       <c r="U11" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="V11" t="n">
         <v>700594</v>
       </c>
       <c r="W11" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.0323026772896258</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0099186377316651</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>2526</v>
       </c>
       <c r="AD11" t="s">
         <v>19</v>
       </c>
       <c r="AE11" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>2542</v>
+        <v>2526</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>2539</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
       <c r="D12" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="E12" t="n">
         <v>205045</v>
@@ -10140,59 +10090,57 @@
         <v>210770</v>
       </c>
       <c r="U12" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="V12" t="n">
         <v>44065</v>
       </c>
       <c r="W12" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.0544176256580924</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0177509607502024</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>2509</v>
       </c>
       <c r="AD12" t="s">
         <v>19</v>
       </c>
       <c r="AE12" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>2545</v>
+        <v>2509</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>2542</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="D13" t="s">
         <v>46</v>
@@ -10246,62 +10194,60 @@
         <v>196190</v>
       </c>
       <c r="U13" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="V13" t="n">
         <v>1000927</v>
       </c>
       <c r="W13" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.0680166096401871</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0216231426788056</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>2536</v>
       </c>
       <c r="AD13" t="s">
         <v>19</v>
       </c>
       <c r="AE13" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AH13" t="n">
+        <v>2536</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" t="b">
+      <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>2547</v>
+      <c r="AH13" t="s">
+        <v>2544</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="D14" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="E14" t="n">
         <v>191306</v>
@@ -10352,62 +10298,60 @@
         <v>212585</v>
       </c>
       <c r="U14" t="s">
-        <v>2550</v>
+        <v>2547</v>
       </c>
       <c r="V14" t="n">
         <v>475769</v>
       </c>
       <c r="W14" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-0.159204207826499</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0495451489695312</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>2548</v>
       </c>
       <c r="AD14" t="s">
         <v>19</v>
       </c>
       <c r="AE14" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AH14" t="n">
+        <v>2548</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0</v>
       </c>
-      <c r="AI14" t="b">
+      <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>2552</v>
+      <c r="AH14" t="s">
+        <v>2549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="D15" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="E15" t="n">
         <v>194498</v>
@@ -10458,59 +10402,57 @@
         <v>196554</v>
       </c>
       <c r="U15" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="V15" t="n">
         <v>423689</v>
       </c>
       <c r="W15" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z15" t="n">
         <v>-0.0985647883335968</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0356788302420697</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>2552</v>
       </c>
       <c r="AD15" t="s">
         <v>19</v>
       </c>
       <c r="AE15" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AH15" t="n">
+        <v>2552</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" t="b">
+      <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>2556</v>
+      <c r="AH15" t="s">
+        <v>2553</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>2557</v>
+        <v>2554</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -10564,62 +10506,60 @@
         <v>196983</v>
       </c>
       <c r="U16" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="V16" t="n">
         <v>294549</v>
       </c>
       <c r="W16" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-0.311334309975924</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.103601065045962</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>2517</v>
       </c>
       <c r="AD16" t="s">
         <v>19</v>
       </c>
       <c r="AE16" t="s">
-        <v>2520</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>2520</v>
-      </c>
-      <c r="AH16" t="n">
+        <v>2517</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" t="b">
+      <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>2558</v>
+      <c r="AH16" t="s">
+        <v>2555</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="D17" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="E17" t="n">
         <v>124644</v>
@@ -10670,62 +10610,60 @@
         <v>210770</v>
       </c>
       <c r="U17" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="V17" t="n">
         <v>26491</v>
       </c>
       <c r="W17" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.413596153679723</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.151806465817754</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>2526</v>
       </c>
       <c r="AD17" t="s">
         <v>19</v>
       </c>
       <c r="AE17" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AH17" t="n">
+        <v>2526</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" t="b">
+      <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>2560</v>
+      <c r="AH17" t="s">
+        <v>2557</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="D18" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="E18" t="n">
         <v>194166</v>
@@ -10776,62 +10714,60 @@
         <v>196554</v>
       </c>
       <c r="U18" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="V18" t="n">
         <v>1004624</v>
       </c>
       <c r="W18" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z18" t="n">
         <v>-0.340968227276485</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.117398373565272</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>2536</v>
       </c>
       <c r="AD18" t="s">
         <v>19</v>
       </c>
       <c r="AE18" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AH18" t="n">
+        <v>2536</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" t="b">
+      <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>2562</v>
+      <c r="AH18" t="s">
+        <v>2559</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
       <c r="D19" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="E19" t="n">
         <v>187466</v>
@@ -10882,62 +10818,60 @@
         <v>196554</v>
       </c>
       <c r="U19" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="V19" t="n">
         <v>861306</v>
       </c>
       <c r="W19" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.22107912396903</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.0804093348388594</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>2526</v>
       </c>
       <c r="AD19" t="s">
         <v>19</v>
       </c>
       <c r="AE19" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AH19" t="n">
+        <v>2526</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" t="b">
+      <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>2564</v>
+      <c r="AH19" t="s">
+        <v>2561</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>2565</v>
+        <v>2562</v>
       </c>
       <c r="D20" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="E20" t="n">
         <v>205045</v>
@@ -10988,62 +10922,60 @@
         <v>210770</v>
       </c>
       <c r="U20" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="V20" t="n">
         <v>552099</v>
       </c>
       <c r="W20" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.230810475134069</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.0890541895508772</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>2517</v>
       </c>
       <c r="AD20" t="s">
         <v>19</v>
       </c>
       <c r="AE20" t="s">
-        <v>2520</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>2520</v>
-      </c>
-      <c r="AH20" t="n">
+        <v>2517</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" t="b">
+      <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>2566</v>
+      <c r="AH20" t="s">
+        <v>2563</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>2567</v>
+        <v>2564</v>
       </c>
       <c r="D21" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="E21" t="n">
         <v>191306</v>
@@ -11094,62 +11026,60 @@
         <v>194166</v>
       </c>
       <c r="U21" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="V21" t="n">
         <v>56482</v>
       </c>
       <c r="W21" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.0805263547719453</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.0285482821269418</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>2536</v>
       </c>
       <c r="AD21" t="s">
         <v>19</v>
       </c>
       <c r="AE21" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AH21" t="n">
+        <v>2536</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" t="b">
+      <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="s">
-        <v>2569</v>
+      <c r="AH21" t="s">
+        <v>2566</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>2570</v>
+        <v>2567</v>
       </c>
       <c r="D22" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="E22" t="n">
         <v>196554</v>
@@ -11200,59 +11130,57 @@
         <v>223618</v>
       </c>
       <c r="U22" t="s">
-        <v>2550</v>
+        <v>2547</v>
       </c>
       <c r="V22" t="n">
         <v>14957</v>
       </c>
       <c r="W22" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z22" t="n">
         <v>-0.184599099330509</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0674427864375972</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>2548</v>
       </c>
       <c r="AD22" t="s">
         <v>19</v>
       </c>
       <c r="AE22" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>2548</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" t="b">
+      <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="s">
-        <v>2572</v>
+      <c r="AH22" t="s">
+        <v>2569</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>2573</v>
+        <v>2570</v>
       </c>
       <c r="D23" t="s">
         <v>78</v>
@@ -11306,62 +11234,60 @@
         <v>192377</v>
       </c>
       <c r="U23" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="V23" t="n">
         <v>554396</v>
       </c>
       <c r="W23" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.24094157351853</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0894384041924952</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>2517</v>
       </c>
       <c r="AD23" t="s">
         <v>19</v>
       </c>
       <c r="AE23" t="s">
-        <v>2520</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>2520</v>
-      </c>
-      <c r="AH23" t="n">
+        <v>2517</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="b">
+      <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>2574</v>
+      <c r="AH23" t="s">
+        <v>2571</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
       <c r="D24" t="s">
-        <v>2576</v>
+        <v>2573</v>
       </c>
       <c r="E24" t="n">
         <v>209424</v>
@@ -11412,62 +11338,60 @@
         <v>214406</v>
       </c>
       <c r="U24" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="V24" t="n">
         <v>369547</v>
       </c>
       <c r="W24" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z24" t="n">
         <v>-0.019026972989752</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.00729457013696255</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>2530</v>
       </c>
       <c r="AD24" t="s">
         <v>19</v>
       </c>
       <c r="AE24" t="s">
-        <v>2533</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>2533</v>
-      </c>
-      <c r="AH24" t="n">
+        <v>2530</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" t="b">
+      <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="s">
-        <v>2577</v>
+      <c r="AH24" t="s">
+        <v>2574</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>2578</v>
+        <v>2575</v>
       </c>
       <c r="D25" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="E25" t="n">
         <v>154915</v>
@@ -11518,62 +11442,60 @@
         <v>207479</v>
       </c>
       <c r="U25" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="V25" t="n">
         <v>423961</v>
       </c>
       <c r="W25" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.0805915434042857</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.0321648024793012</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>2536</v>
       </c>
       <c r="AD25" t="s">
         <v>19</v>
       </c>
       <c r="AE25" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AH25" t="n">
+        <v>2536</v>
+      </c>
+      <c r="AF25" t="n">
         <v>0</v>
       </c>
-      <c r="AI25" t="b">
+      <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="s">
-        <v>2578</v>
+      <c r="AH25" t="s">
+        <v>2575</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>2580</v>
+        <v>2577</v>
       </c>
       <c r="D26" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="E26" t="n">
         <v>198538</v>
@@ -11624,62 +11546,60 @@
         <v>223618</v>
       </c>
       <c r="U26" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="V26" t="n">
         <v>20978</v>
       </c>
       <c r="W26" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.0397332212175659</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.0155012377134709</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>2536</v>
       </c>
       <c r="AD26" t="s">
         <v>19</v>
       </c>
       <c r="AE26" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>2539</v>
-      </c>
-      <c r="AH26" t="n">
+        <v>2536</v>
+      </c>
+      <c r="AF26" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" t="b">
+      <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="s">
-        <v>2581</v>
+      <c r="AH26" t="s">
+        <v>2578</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="D27" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="E27" t="n">
         <v>134626</v>
@@ -11730,62 +11650,60 @@
         <v>196554</v>
       </c>
       <c r="U27" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="V27" t="n">
         <v>986779</v>
       </c>
       <c r="W27" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z27" t="n">
         <v>-0.198672451427276</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.0805943503943729</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>2512</v>
       </c>
       <c r="AD27" t="s">
         <v>19</v>
       </c>
       <c r="AE27" t="s">
-        <v>2515</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>2515</v>
-      </c>
-      <c r="AH27" t="n">
+        <v>2512</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" t="b">
+      <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="s">
-        <v>2583</v>
+      <c r="AH27" t="s">
+        <v>2580</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>2584</v>
+        <v>2581</v>
       </c>
       <c r="D28" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="E28" t="n">
         <v>195272</v>
@@ -11836,62 +11754,60 @@
         <v>198538</v>
       </c>
       <c r="U28" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
       <c r="V28" t="n">
         <v>253309</v>
       </c>
       <c r="W28" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
       </c>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Y28" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z28" t="n">
         <v>-0.229405483420418</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AA28" t="n">
         <v>0.0906326551529214</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>2583</v>
       </c>
       <c r="AD28" t="s">
         <v>19</v>
       </c>
       <c r="AE28" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AH28" t="n">
+        <v>2583</v>
+      </c>
+      <c r="AF28" t="n">
         <v>0</v>
       </c>
-      <c r="AI28" t="b">
+      <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="s">
-        <v>2584</v>
+      <c r="AH28" t="s">
+        <v>2581</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>2587</v>
+        <v>2584</v>
       </c>
       <c r="D29" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="E29" t="n">
         <v>191306</v>
@@ -11942,62 +11858,60 @@
         <v>209424</v>
       </c>
       <c r="U29" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="V29" t="n">
         <v>119413</v>
       </c>
       <c r="W29" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="Y29" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z29" t="n">
         <v>-0.070266704523201</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AA29" t="n">
         <v>0.0286457429870539</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>2587</v>
       </c>
       <c r="AD29" t="s">
         <v>19</v>
       </c>
       <c r="AE29" t="s">
-        <v>2590</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>2590</v>
-      </c>
-      <c r="AH29" t="n">
+        <v>2587</v>
+      </c>
+      <c r="AF29" t="n">
         <v>0</v>
       </c>
-      <c r="AI29" t="b">
+      <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="s">
-        <v>2591</v>
+      <c r="AH29" t="s">
+        <v>2588</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>2592</v>
+        <v>2589</v>
       </c>
       <c r="D30" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="E30" t="n">
         <v>192377</v>
@@ -12048,59 +11962,57 @@
         <v>198538</v>
       </c>
       <c r="U30" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="V30" t="n">
         <v>921860</v>
       </c>
       <c r="W30" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
       </c>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="Y30" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z30" t="n">
         <v>-0.308369222176951</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AA30" t="n">
         <v>0.126971279910773</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>2526</v>
       </c>
       <c r="AD30" t="s">
         <v>19</v>
       </c>
       <c r="AE30" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AH30" t="n">
+        <v>2526</v>
+      </c>
+      <c r="AF30" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" t="b">
+      <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="s">
-        <v>2593</v>
+      <c r="AH30" t="s">
+        <v>2590</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>2594</v>
+        <v>2591</v>
       </c>
       <c r="D31" t="s">
         <v>107</v>
@@ -12154,59 +12066,57 @@
         <v>193011</v>
       </c>
       <c r="U31" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="V31" t="n">
         <v>1159488</v>
       </c>
       <c r="W31" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="Y31" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z31" t="n">
         <v>-0.350809958406873</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AA31" t="n">
         <v>0.145252281336878</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>2509</v>
       </c>
       <c r="AD31" t="s">
         <v>19</v>
       </c>
       <c r="AE31" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>2512</v>
-      </c>
-      <c r="AH31" t="n">
+        <v>2509</v>
+      </c>
+      <c r="AF31" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" t="b">
+      <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>2595</v>
+      <c r="AH31" t="s">
+        <v>2592</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>2596</v>
+        <v>2593</v>
       </c>
       <c r="D32" t="s">
         <v>107</v>
@@ -12260,62 +12170,60 @@
         <v>193011</v>
       </c>
       <c r="U32" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="V32" t="n">
         <v>679357</v>
       </c>
       <c r="W32" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
       </c>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="Y32" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.0535758897852804</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AA32" t="n">
         <v>0.0209992563317506</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>2512</v>
       </c>
       <c r="AD32" t="s">
         <v>19</v>
       </c>
       <c r="AE32" t="s">
-        <v>2515</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>2515</v>
-      </c>
-      <c r="AH32" t="n">
+        <v>2512</v>
+      </c>
+      <c r="AF32" t="n">
         <v>0</v>
       </c>
-      <c r="AI32" t="b">
+      <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="s">
-        <v>2597</v>
+      <c r="AH32" t="s">
+        <v>2594</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="D33" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="E33" t="n">
         <v>194166</v>
@@ -12366,62 +12274,60 @@
         <v>196554</v>
       </c>
       <c r="U33" t="s">
-        <v>2550</v>
+        <v>2547</v>
       </c>
       <c r="V33" t="n">
         <v>770801</v>
       </c>
       <c r="W33" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
       </c>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="Y33" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z33" t="n">
         <v>-0.205459466219342</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AA33" t="n">
         <v>0.0804214935345212</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>2548</v>
       </c>
       <c r="AD33" t="s">
         <v>19</v>
       </c>
       <c r="AE33" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>2551</v>
-      </c>
-      <c r="AH33" t="n">
+        <v>2548</v>
+      </c>
+      <c r="AF33" t="n">
         <v>0</v>
       </c>
-      <c r="AI33" t="b">
+      <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="s">
-        <v>2599</v>
+      <c r="AH33" t="s">
+        <v>2596</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="D34" t="s">
-        <v>2601</v>
+        <v>2598</v>
       </c>
       <c r="E34" t="n">
         <v>194498</v>
@@ -12472,59 +12378,57 @@
         <v>213822</v>
       </c>
       <c r="U34" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
       <c r="V34" t="n">
         <v>182159</v>
       </c>
       <c r="W34" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
       </c>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="Y34" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z34" t="n">
         <v>-0.147371542889311</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AA34" t="n">
         <v>0.0613073467112781</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>2583</v>
       </c>
       <c r="AD34" t="s">
         <v>19</v>
       </c>
       <c r="AE34" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>2586</v>
-      </c>
-      <c r="AH34" t="n">
+        <v>2583</v>
+      </c>
+      <c r="AF34" t="n">
         <v>0</v>
       </c>
-      <c r="AI34" t="b">
+      <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="s">
-        <v>2602</v>
+      <c r="AH34" t="s">
+        <v>2599</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B35" t="s">
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>2603</v>
+        <v>2600</v>
       </c>
       <c r="D35" t="s">
         <v>91</v>
@@ -12578,62 +12482,60 @@
         <v>222592</v>
       </c>
       <c r="U35" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="V35" t="n">
         <v>155222</v>
       </c>
       <c r="W35" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
       </c>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="Y35" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z35" t="n">
         <v>-0.0997717898983886</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AA35" t="n">
         <v>0.0414841015251748</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>2552</v>
       </c>
       <c r="AD35" t="s">
         <v>19</v>
       </c>
       <c r="AE35" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AH35" t="n">
+        <v>2552</v>
+      </c>
+      <c r="AF35" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" t="b">
+      <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="s">
-        <v>2604</v>
+      <c r="AH35" t="s">
+        <v>2601</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>2605</v>
+        <v>2602</v>
       </c>
       <c r="D36" t="s">
-        <v>2606</v>
+        <v>2603</v>
       </c>
       <c r="E36" t="n">
         <v>222592</v>
@@ -12684,59 +12586,57 @@
         <v>234669</v>
       </c>
       <c r="U36" t="s">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="V36" t="n">
         <v>552770</v>
       </c>
       <c r="W36" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
       </c>
-      <c r="Y36"/>
-      <c r="Z36"/>
-      <c r="AA36" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="Y36" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z36" t="n">
         <v>-0.162386877375938</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AA36" t="n">
         <v>0.0880655449435537</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>2605</v>
       </c>
       <c r="AD36" t="s">
         <v>19</v>
       </c>
       <c r="AE36" t="s">
-        <v>2608</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>2608</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>2609</v>
+        <v>2605</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>2606</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>2610</v>
+        <v>2607</v>
       </c>
       <c r="D37" t="s">
         <v>14</v>
@@ -12790,59 +12690,57 @@
         <v>196983</v>
       </c>
       <c r="U37" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="V37" t="n">
         <v>830939</v>
       </c>
       <c r="W37" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
       </c>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AA37" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="Y37" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z37" t="n">
         <v>0.0903743959569218</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AA37" t="n">
         <v>0.0397044536463002</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>2512</v>
       </c>
       <c r="AD37" t="s">
         <v>19</v>
       </c>
       <c r="AE37" t="s">
-        <v>2515</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>2515</v>
-      </c>
-      <c r="AH37" t="n">
+        <v>2512</v>
+      </c>
+      <c r="AF37" t="n">
         <v>0</v>
       </c>
-      <c r="AI37" t="b">
+      <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AJ37" t="s">
-        <v>2611</v>
+      <c r="AH37" t="s">
+        <v>2608</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B38" t="s">
         <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>2612</v>
+        <v>2609</v>
       </c>
       <c r="D38" t="s">
         <v>107</v>
@@ -12896,62 +12794,60 @@
         <v>193011</v>
       </c>
       <c r="U38" t="s">
-        <v>2613</v>
+        <v>2610</v>
       </c>
       <c r="V38" t="n">
         <v>139364</v>
       </c>
       <c r="W38" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
       </c>
-      <c r="Y38"/>
-      <c r="Z38"/>
-      <c r="AA38" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="Y38" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z38" t="n">
         <v>-0.0739764659284659</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AA38" t="n">
         <v>0.0306469186862317</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>2611</v>
       </c>
       <c r="AD38" t="s">
         <v>19</v>
       </c>
       <c r="AE38" t="s">
-        <v>2614</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>2614</v>
-      </c>
-      <c r="AH38" t="n">
+        <v>2611</v>
+      </c>
+      <c r="AF38" t="n">
         <v>0</v>
       </c>
-      <c r="AI38" t="b">
+      <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="s">
-        <v>2615</v>
+      <c r="AH38" t="s">
+        <v>2612</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>2616</v>
+        <v>2613</v>
       </c>
       <c r="D39" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="E39" t="n">
         <v>178287</v>
@@ -13002,62 +12898,60 @@
         <v>194166</v>
       </c>
       <c r="U39" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="V39" t="n">
         <v>498096</v>
       </c>
       <c r="W39" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
       </c>
-      <c r="Y39"/>
-      <c r="Z39"/>
-      <c r="AA39" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="Y39" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z39" t="n">
         <v>0.0432535564168672</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AA39" t="n">
         <v>0.0228873548548558</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>2526</v>
       </c>
       <c r="AD39" t="s">
         <v>19</v>
       </c>
       <c r="AE39" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>2529</v>
-      </c>
-      <c r="AH39" t="n">
+        <v>2526</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0</v>
       </c>
-      <c r="AI39" t="b">
+      <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="s">
-        <v>2617</v>
+      <c r="AH39" t="s">
+        <v>2614</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B40" t="s">
         <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>2618</v>
+        <v>2615</v>
       </c>
       <c r="D40" t="s">
-        <v>2619</v>
+        <v>2616</v>
       </c>
       <c r="E40" t="n">
         <v>193011</v>
@@ -13108,59 +13002,57 @@
         <v>194498</v>
       </c>
       <c r="U40" t="s">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="V40" t="n">
         <v>515063</v>
       </c>
       <c r="W40" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X40" t="b">
         <v>1</v>
       </c>
-      <c r="Y40"/>
-      <c r="Z40"/>
-      <c r="AA40" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="Y40" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z40" t="n">
         <v>-0.0991382907229282</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AA40" t="n">
         <v>0.0447668793372665</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>2605</v>
       </c>
       <c r="AD40" t="s">
         <v>19</v>
       </c>
       <c r="AE40" t="s">
-        <v>2608</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>2608</v>
-      </c>
-      <c r="AH40" t="n">
+        <v>2605</v>
+      </c>
+      <c r="AF40" t="n">
         <v>0</v>
       </c>
-      <c r="AI40" t="b">
+      <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="s">
-        <v>2620</v>
+      <c r="AH40" t="s">
+        <v>2617</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B41" t="s">
         <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="D41" t="s">
         <v>14</v>
@@ -13214,62 +13106,60 @@
         <v>196983</v>
       </c>
       <c r="U41" t="s">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="V41" t="n">
         <v>369891</v>
       </c>
       <c r="W41" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X41" t="b">
         <v>1</v>
       </c>
-      <c r="Y41"/>
-      <c r="Z41"/>
-      <c r="AA41" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="Y41" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z41" t="n">
         <v>-0.0982199656864866</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AA41" t="n">
         <v>0.0411139349267222</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>2605</v>
       </c>
       <c r="AD41" t="s">
         <v>19</v>
       </c>
       <c r="AE41" t="s">
-        <v>2608</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>2608</v>
-      </c>
-      <c r="AH41" t="n">
+        <v>2605</v>
+      </c>
+      <c r="AF41" t="n">
         <v>0</v>
       </c>
-      <c r="AI41" t="b">
+      <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="s">
-        <v>2622</v>
+      <c r="AH41" t="s">
+        <v>2619</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="B42" t="s">
         <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>2623</v>
+        <v>2620</v>
       </c>
       <c r="D42" t="s">
-        <v>2624</v>
+        <v>2621</v>
       </c>
       <c r="E42" t="n">
         <v>215862</v>
@@ -13320,48 +13210,46 @@
         <v>225229</v>
       </c>
       <c r="U42" t="s">
-        <v>2625</v>
+        <v>2622</v>
       </c>
       <c r="V42" t="n">
         <v>429466</v>
       </c>
       <c r="W42" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="X42" t="b">
         <v>1</v>
       </c>
-      <c r="Y42"/>
-      <c r="Z42"/>
-      <c r="AA42" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="Y42" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Z42" t="n">
         <v>0.20816354370558</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AA42" t="n">
         <v>0.130930858466448</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>2623</v>
       </c>
       <c r="AD42" t="s">
         <v>19</v>
       </c>
       <c r="AE42" t="s">
-        <v>2626</v>
-      </c>
-      <c r="AF42" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>2626</v>
-      </c>
-      <c r="AH42" t="n">
+        <v>2623</v>
+      </c>
+      <c r="AF42" t="n">
         <v>3</v>
       </c>
-      <c r="AI42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>2627</v>
+      <c r="AG42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>2624</v>
       </c>
     </row>
   </sheetData>
@@ -13440,37 +13328,28 @@
         <v>2493</v>
       </c>
       <c r="V1" t="s">
-        <v>2628</v>
+        <v>41</v>
       </c>
       <c r="W1" t="s">
-        <v>2629</v>
+        <v>2497</v>
       </c>
       <c r="X1" t="s">
-        <v>2630</v>
+        <v>2498</v>
       </c>
       <c r="Y1" t="s">
-        <v>2631</v>
+        <v>2499</v>
       </c>
       <c r="Z1" t="s">
-        <v>2632</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="AB1" t="s">
-        <v>2502</v>
+        <v>2625</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>2503</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>2633</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>2506</v>
       </c>
     </row>
     <row r="2">
@@ -13478,7 +13357,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>2634</v>
+        <v>2626</v>
       </c>
       <c r="C2" t="s">
         <v>102</v>
@@ -13538,37 +13417,28 @@
         <v>138829</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.7244467938385</v>
+        <v>-0.0738987436476202</v>
       </c>
       <c r="W2" t="n">
-        <v>-3.40419343898807</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-4.54243715912387</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-4.07962719921153</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-5.16845520098768</v>
+        <v>0.0167496410319448</v>
+      </c>
+      <c r="X2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>19</v>
       </c>
       <c r="AA2" t="s">
         <v>19</v>
       </c>
-      <c r="AB2" t="s">
-        <v>19</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>2635</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="3">
@@ -13576,10 +13446,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>2636</v>
+        <v>2628</v>
       </c>
       <c r="C3" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="D3" t="n">
         <v>196190</v>
@@ -13636,37 +13506,28 @@
         <v>201076</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.23015412677998</v>
+        <v>-0.0377740052482749</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.1007453826805</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.50199568172443</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-1.73752001877129</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-3.2639043215063</v>
+        <v>0.0190832891724736</v>
+      </c>
+      <c r="X3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>19</v>
       </c>
       <c r="AA3" t="s">
         <v>19</v>
       </c>
-      <c r="AB3" t="s">
-        <v>19</v>
+      <c r="AB3" t="n">
+        <v>0.00179910044977511</v>
       </c>
       <c r="AC3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.00179910044977511</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>2637</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="4">
@@ -13674,10 +13535,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>2638</v>
+        <v>2630</v>
       </c>
       <c r="C4" t="s">
-        <v>2639</v>
+        <v>2631</v>
       </c>
       <c r="D4" t="n">
         <v>8258</v>
@@ -13734,37 +13595,28 @@
         <v>141892</v>
       </c>
       <c r="V4" t="n">
-        <v>0.120227373215467</v>
+        <v>-0.00634239074174681</v>
       </c>
       <c r="W4" t="n">
-        <v>3.70509586013993</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.1651485050526</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1.14414324565653</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-0.873874333427764</v>
+        <v>0.0812261356895586</v>
+      </c>
+      <c r="X4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>19</v>
       </c>
       <c r="AA4" t="s">
         <v>19</v>
       </c>
-      <c r="AB4" t="s">
-        <v>19</v>
+      <c r="AB4" t="n">
+        <v>0.0049792531120332</v>
       </c>
       <c r="AC4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.0049792531120332</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>2640</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="5">
@@ -13772,10 +13624,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>2641</v>
+        <v>2633</v>
       </c>
       <c r="C5" t="s">
-        <v>2642</v>
+        <v>2634</v>
       </c>
       <c r="D5" t="n">
         <v>248286</v>
@@ -13832,37 +13684,28 @@
         <v>178841</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.77868514516594</v>
+        <v>-0.163267648519762</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.14643319865102</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-3.02897554990424</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-1.36859844124524</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-1.73577430355832</v>
+        <v>0.0897251233924304</v>
+      </c>
+      <c r="X5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>19</v>
       </c>
       <c r="AA5" t="s">
         <v>19</v>
       </c>
-      <c r="AB5" t="s">
-        <v>19</v>
+      <c r="AB5" t="n">
+        <v>0.010379746835443</v>
       </c>
       <c r="AC5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.010379746835443</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>2643</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="6">
@@ -13870,10 +13713,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>2644</v>
+        <v>2636</v>
       </c>
       <c r="C6" t="s">
-        <v>2645</v>
+        <v>2637</v>
       </c>
       <c r="D6" t="n">
         <v>81128</v>
@@ -13930,37 +13773,28 @@
         <v>144327</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.63426788512135</v>
+        <v>-0.103299317243678</v>
       </c>
       <c r="W6" t="n">
-        <v>1.50453866549048</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2.88647266609856</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-2.5910333102638</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.609342444066655</v>
+        <v>0.102903705955469</v>
+      </c>
+      <c r="X6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>19</v>
       </c>
       <c r="AA6" t="s">
         <v>19</v>
       </c>
-      <c r="AB6" t="s">
-        <v>19</v>
+      <c r="AB6" t="n">
+        <v>0.0115365298229429</v>
       </c>
       <c r="AC6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.0115365298229429</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>2646</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="7">
@@ -13968,10 +13802,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>2647</v>
+        <v>2639</v>
       </c>
       <c r="C7" t="s">
-        <v>2648</v>
+        <v>2640</v>
       </c>
       <c r="D7" t="n">
         <v>408422</v>
@@ -14028,37 +13862,28 @@
         <v>150181</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.90490322830344</v>
+        <v>-0.0134443799031584</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.15978890903048</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.721248042505301</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.666316903621503</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.50572473245652</v>
+        <v>0.0325177254152698</v>
+      </c>
+      <c r="X7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>19</v>
       </c>
       <c r="AA7" t="s">
         <v>19</v>
       </c>
-      <c r="AB7" t="s">
-        <v>19</v>
+      <c r="AB7" t="n">
+        <v>0.0199320498301246</v>
       </c>
       <c r="AC7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.0199320498301246</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>2649</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="8">
@@ -14066,7 +13891,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="C8" t="s">
         <v>63</v>
@@ -14126,37 +13951,28 @@
         <v>156803</v>
       </c>
       <c r="V8" t="n">
-        <v>0.980759384992158</v>
+        <v>0.00141871225672319</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.55959452897391</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.375859393185138</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3.22413287387525</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-1.7403289092336</v>
+        <v>0.0404091101584064</v>
+      </c>
+      <c r="X8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>19</v>
       </c>
       <c r="AA8" t="s">
         <v>19</v>
       </c>
-      <c r="AB8" t="s">
-        <v>19</v>
+      <c r="AB8" t="n">
+        <v>0.0199320498301246</v>
       </c>
       <c r="AC8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.0199320498301246</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>2651</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="9">
@@ -14164,10 +13980,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>2652</v>
+        <v>2644</v>
       </c>
       <c r="C9" t="s">
-        <v>2653</v>
+        <v>2645</v>
       </c>
       <c r="D9" t="n">
         <v>488835</v>
@@ -14224,37 +14040,28 @@
         <v>148599</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.07247199216459</v>
+        <v>-0.0602507300903937</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.32475719517037</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-2.71982477043598</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.391684328550726</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-1.70768842125269</v>
+        <v>0.0357253906453629</v>
+      </c>
+      <c r="X9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>19</v>
       </c>
       <c r="AA9" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" t="s">
-        <v>19</v>
+      <c r="AB9" t="n">
+        <v>0.0239875841757128</v>
       </c>
       <c r="AC9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.0239875841757128</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>2654</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="10">
@@ -14262,10 +14069,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>2655</v>
+        <v>2647</v>
       </c>
       <c r="C10" t="s">
-        <v>2656</v>
+        <v>2648</v>
       </c>
       <c r="D10" t="n">
         <v>117072</v>
@@ -14322,37 +14129,28 @@
         <v>164527</v>
       </c>
       <c r="V10" t="n">
-        <v>0.775383105099076</v>
+        <v>0.0335376295967299</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12980880455261</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-3.01630381119073</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-0.353058812819829</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.2162968562434</v>
+        <v>0.143369386905559</v>
+      </c>
+      <c r="X10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>19</v>
       </c>
       <c r="AA10" t="s">
         <v>19</v>
       </c>
-      <c r="AB10" t="s">
-        <v>19</v>
+      <c r="AB10" t="n">
+        <v>0.0258520957551904</v>
       </c>
       <c r="AC10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.0258520957551904</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>2657</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="11">
@@ -14360,10 +14158,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>2658</v>
+        <v>2650</v>
       </c>
       <c r="C11" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D11" t="n">
         <v>124644</v>
@@ -14420,37 +14218,28 @@
         <v>146951</v>
       </c>
       <c r="V11" t="n">
-        <v>2.17180083682997</v>
+        <v>0.0808099763992987</v>
       </c>
       <c r="W11" t="n">
-        <v>0.601533678578033</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.38961507498467</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-1.36273642785685</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-1.38306942310534</v>
+        <v>0.116491317024866</v>
+      </c>
+      <c r="X11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>19</v>
       </c>
       <c r="AA11" t="s">
         <v>19</v>
       </c>
-      <c r="AB11" t="s">
-        <v>19</v>
+      <c r="AB11" t="n">
+        <v>0.0490422236988918</v>
       </c>
       <c r="AC11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.0490422236988918</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>2659</v>
+        <v>2651</v>
       </c>
     </row>
   </sheetData>
@@ -14481,34 +14270,34 @@
         <v>28</v>
       </c>
       <c r="F1" t="s">
-        <v>2660</v>
+        <v>2652</v>
       </c>
       <c r="G1" t="s">
         <v>946</v>
       </c>
       <c r="H1" t="s">
-        <v>2661</v>
+        <v>2653</v>
       </c>
       <c r="I1" t="s">
-        <v>2662</v>
+        <v>2654</v>
       </c>
       <c r="J1" t="s">
         <v>956</v>
       </c>
       <c r="K1" t="s">
-        <v>2663</v>
+        <v>2655</v>
       </c>
       <c r="L1" t="s">
-        <v>2664</v>
+        <v>2656</v>
       </c>
       <c r="M1" t="s">
-        <v>2665</v>
+        <v>2657</v>
       </c>
       <c r="N1" t="s">
-        <v>2666</v>
+        <v>2658</v>
       </c>
       <c r="O1" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="P1" t="s">
         <v>2493</v>
@@ -14528,33 +14317,33 @@
         <v>2115</v>
       </c>
       <c r="E2" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F2" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G2" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>2670</v>
+        <v>2662</v>
       </c>
       <c r="K2" t="s">
-        <v>2671</v>
+        <v>2663</v>
       </c>
       <c r="L2" t="s">
-        <v>2670</v>
+        <v>2662</v>
       </c>
       <c r="M2" t="s">
-        <v>2672</v>
+        <v>2664</v>
       </c>
       <c r="N2" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O2" t="s">
-        <v>2674</v>
+        <v>2666</v>
       </c>
       <c r="P2" t="n">
         <v>134177</v>
@@ -14574,30 +14363,30 @@
         <v>408</v>
       </c>
       <c r="E3" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G3" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>2676</v>
+        <v>2668</v>
       </c>
       <c r="K3" t="s">
-        <v>2677</v>
+        <v>2669</v>
       </c>
       <c r="L3" t="s">
-        <v>2676</v>
+        <v>2668</v>
       </c>
       <c r="M3" t="s">
-        <v>2678</v>
+        <v>2670</v>
       </c>
       <c r="N3" t="s">
-        <v>2679</v>
+        <v>2671</v>
       </c>
       <c r="O3"/>
       <c r="P3" t="n">
@@ -14618,33 +14407,33 @@
         <v>846</v>
       </c>
       <c r="E4" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G4" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>2634</v>
+        <v>2626</v>
       </c>
       <c r="K4" t="s">
-        <v>2680</v>
+        <v>2672</v>
       </c>
       <c r="L4" t="s">
-        <v>2634</v>
+        <v>2626</v>
       </c>
       <c r="M4" t="s">
-        <v>2681</v>
+        <v>2673</v>
       </c>
       <c r="N4" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O4" t="s">
-        <v>2635</v>
+        <v>2627</v>
       </c>
       <c r="P4" t="n">
         <v>139340</v>
@@ -14664,30 +14453,30 @@
         <v>381</v>
       </c>
       <c r="E5" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F5" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G5" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>2682</v>
+        <v>2674</v>
       </c>
       <c r="K5" t="s">
-        <v>2683</v>
+        <v>2675</v>
       </c>
       <c r="L5" t="s">
-        <v>2682</v>
+        <v>2674</v>
       </c>
       <c r="M5" t="s">
-        <v>2678</v>
+        <v>2670</v>
       </c>
       <c r="N5" t="s">
-        <v>2679</v>
+        <v>2671</v>
       </c>
       <c r="O5"/>
       <c r="P5" t="n">
@@ -14708,33 +14497,33 @@
         <v>2001</v>
       </c>
       <c r="E6" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F6" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G6" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>2638</v>
+        <v>2630</v>
       </c>
       <c r="K6" t="s">
-        <v>2684</v>
+        <v>2676</v>
       </c>
       <c r="L6" t="s">
-        <v>2638</v>
+        <v>2630</v>
       </c>
       <c r="M6" t="s">
-        <v>2685</v>
+        <v>2677</v>
       </c>
       <c r="N6" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O6" t="s">
-        <v>2640</v>
+        <v>2632</v>
       </c>
       <c r="P6" t="n">
         <v>142892</v>
@@ -14754,33 +14543,33 @@
         <v>1008</v>
       </c>
       <c r="E7" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F7" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G7" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>2644</v>
+        <v>2636</v>
       </c>
       <c r="K7" t="s">
-        <v>2686</v>
+        <v>2678</v>
       </c>
       <c r="L7" t="s">
-        <v>2644</v>
+        <v>2636</v>
       </c>
       <c r="M7" t="s">
-        <v>2687</v>
+        <v>2679</v>
       </c>
       <c r="N7" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O7" t="s">
-        <v>2646</v>
+        <v>2638</v>
       </c>
       <c r="P7" t="n">
         <v>144830</v>
@@ -14800,33 +14589,33 @@
         <v>849</v>
       </c>
       <c r="E8" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G8" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>2688</v>
+        <v>2680</v>
       </c>
       <c r="K8" t="s">
-        <v>2689</v>
+        <v>2681</v>
       </c>
       <c r="L8" t="s">
-        <v>2688</v>
+        <v>2680</v>
       </c>
       <c r="M8" t="s">
-        <v>2690</v>
+        <v>2682</v>
       </c>
       <c r="N8" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O8" t="s">
-        <v>2691</v>
+        <v>2683</v>
       </c>
       <c r="P8" t="n">
         <v>146331</v>
@@ -14846,33 +14635,33 @@
         <v>1029</v>
       </c>
       <c r="E9" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F9" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G9" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>2658</v>
+        <v>2650</v>
       </c>
       <c r="K9" t="s">
-        <v>2692</v>
+        <v>2684</v>
       </c>
       <c r="L9" t="s">
-        <v>2658</v>
+        <v>2650</v>
       </c>
       <c r="M9" t="s">
-        <v>2693</v>
+        <v>2685</v>
       </c>
       <c r="N9" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O9" t="s">
-        <v>2659</v>
+        <v>2651</v>
       </c>
       <c r="P9" t="n">
         <v>147465</v>
@@ -14892,33 +14681,33 @@
         <v>424</v>
       </c>
       <c r="E10" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F10" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G10" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>2694</v>
+        <v>2686</v>
       </c>
       <c r="K10" t="s">
-        <v>2695</v>
+        <v>2687</v>
       </c>
       <c r="L10" t="s">
-        <v>2694</v>
+        <v>2686</v>
       </c>
       <c r="M10" t="s">
-        <v>2696</v>
+        <v>2688</v>
       </c>
       <c r="N10" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O10" t="s">
-        <v>2697</v>
+        <v>2689</v>
       </c>
       <c r="P10" t="n">
         <v>148388</v>
@@ -14938,33 +14727,33 @@
         <v>1293</v>
       </c>
       <c r="E11" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G11" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>2652</v>
+        <v>2644</v>
       </c>
       <c r="K11" t="s">
-        <v>2698</v>
+        <v>2690</v>
       </c>
       <c r="L11" t="s">
-        <v>2652</v>
+        <v>2644</v>
       </c>
       <c r="M11" t="s">
-        <v>2699</v>
+        <v>2691</v>
       </c>
       <c r="N11" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O11" t="s">
-        <v>2654</v>
+        <v>2646</v>
       </c>
       <c r="P11" t="n">
         <v>149368</v>
@@ -14984,33 +14773,33 @@
         <v>678</v>
       </c>
       <c r="E12" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G12" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>2647</v>
+        <v>2639</v>
       </c>
       <c r="K12" t="s">
-        <v>2700</v>
+        <v>2692</v>
       </c>
       <c r="L12" t="s">
-        <v>2647</v>
+        <v>2639</v>
       </c>
       <c r="M12" t="s">
-        <v>2701</v>
+        <v>2693</v>
       </c>
       <c r="N12" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O12" t="s">
-        <v>2649</v>
+        <v>2641</v>
       </c>
       <c r="P12" t="n">
         <v>150640</v>
@@ -15030,33 +14819,33 @@
         <v>2289</v>
       </c>
       <c r="E13" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F13" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G13" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>2702</v>
+        <v>2694</v>
       </c>
       <c r="K13" t="s">
-        <v>2703</v>
+        <v>2695</v>
       </c>
       <c r="L13" t="s">
-        <v>2702</v>
+        <v>2694</v>
       </c>
       <c r="M13" t="s">
-        <v>2704</v>
+        <v>2696</v>
       </c>
       <c r="N13" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O13" t="s">
-        <v>2705</v>
+        <v>2697</v>
       </c>
       <c r="P13" t="n">
         <v>154664</v>
@@ -15076,33 +14865,33 @@
         <v>696</v>
       </c>
       <c r="E14" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F14" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G14" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="K14" t="s">
-        <v>2706</v>
+        <v>2698</v>
       </c>
       <c r="L14" t="s">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="M14" t="s">
-        <v>2707</v>
+        <v>2699</v>
       </c>
       <c r="N14" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O14" t="s">
-        <v>2651</v>
+        <v>2643</v>
       </c>
       <c r="P14" t="n">
         <v>157150</v>
@@ -15122,33 +14911,33 @@
         <v>1383</v>
       </c>
       <c r="E15" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G15" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>2708</v>
+        <v>2700</v>
       </c>
       <c r="K15" t="s">
-        <v>2709</v>
+        <v>2701</v>
       </c>
       <c r="L15" t="s">
-        <v>2708</v>
+        <v>2700</v>
       </c>
       <c r="M15" t="s">
-        <v>2710</v>
+        <v>2702</v>
       </c>
       <c r="N15" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O15" t="s">
-        <v>2711</v>
+        <v>2703</v>
       </c>
       <c r="P15" t="n">
         <v>158427</v>
@@ -15168,33 +14957,33 @@
         <v>696</v>
       </c>
       <c r="E16" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F16" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G16" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>2712</v>
+        <v>2704</v>
       </c>
       <c r="K16" t="s">
-        <v>2713</v>
+        <v>2705</v>
       </c>
       <c r="L16" t="s">
-        <v>2712</v>
+        <v>2704</v>
       </c>
       <c r="M16" t="s">
-        <v>2701</v>
+        <v>2693</v>
       </c>
       <c r="N16" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O16" t="s">
-        <v>2714</v>
+        <v>2706</v>
       </c>
       <c r="P16" t="n">
         <v>159928</v>
@@ -15214,33 +15003,33 @@
         <v>1893</v>
       </c>
       <c r="E17" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F17" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G17" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>2715</v>
+        <v>2707</v>
       </c>
       <c r="K17" t="s">
-        <v>2716</v>
+        <v>2708</v>
       </c>
       <c r="L17" t="s">
-        <v>2715</v>
+        <v>2707</v>
       </c>
       <c r="M17" t="s">
-        <v>2717</v>
+        <v>2709</v>
       </c>
       <c r="N17" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O17" t="s">
-        <v>2718</v>
+        <v>2710</v>
       </c>
       <c r="P17" t="n">
         <v>161496</v>
@@ -15260,33 +15049,33 @@
         <v>1563</v>
       </c>
       <c r="E18" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F18" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G18" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>2719</v>
+        <v>2711</v>
       </c>
       <c r="K18" t="s">
-        <v>2720</v>
+        <v>2712</v>
       </c>
       <c r="L18" t="s">
-        <v>2719</v>
+        <v>2711</v>
       </c>
       <c r="M18" t="s">
-        <v>2721</v>
+        <v>2713</v>
       </c>
       <c r="N18" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O18" t="s">
-        <v>2722</v>
+        <v>2714</v>
       </c>
       <c r="P18" t="n">
         <v>163504</v>
@@ -15306,33 +15095,33 @@
         <v>1557</v>
       </c>
       <c r="E19" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F19" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G19" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>2655</v>
+        <v>2647</v>
       </c>
       <c r="K19" t="s">
-        <v>2723</v>
+        <v>2715</v>
       </c>
       <c r="L19" t="s">
-        <v>2655</v>
+        <v>2647</v>
       </c>
       <c r="M19" t="s">
-        <v>2724</v>
+        <v>2716</v>
       </c>
       <c r="N19" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O19" t="s">
-        <v>2657</v>
+        <v>2649</v>
       </c>
       <c r="P19" t="n">
         <v>165305</v>
@@ -15352,33 +15141,33 @@
         <v>649</v>
       </c>
       <c r="E20" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F20" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G20" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>2725</v>
+        <v>2717</v>
       </c>
       <c r="K20" t="s">
-        <v>2726</v>
+        <v>2718</v>
       </c>
       <c r="L20" t="s">
-        <v>2725</v>
+        <v>2717</v>
       </c>
       <c r="M20" t="s">
-        <v>2727</v>
+        <v>2719</v>
       </c>
       <c r="N20" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O20" t="s">
-        <v>2728</v>
+        <v>2720</v>
       </c>
       <c r="P20" t="n">
         <v>166561</v>
@@ -15398,33 +15187,33 @@
         <v>4011</v>
       </c>
       <c r="E21" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F21" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G21" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>2729</v>
+        <v>2721</v>
       </c>
       <c r="K21" t="s">
-        <v>2730</v>
+        <v>2722</v>
       </c>
       <c r="L21" t="s">
-        <v>2729</v>
+        <v>2721</v>
       </c>
       <c r="M21" t="s">
-        <v>2731</v>
+        <v>2723</v>
       </c>
       <c r="N21" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O21" t="s">
-        <v>2732</v>
+        <v>2724</v>
       </c>
       <c r="P21" t="n">
         <v>169813</v>
@@ -15444,33 +15233,33 @@
         <v>378</v>
       </c>
       <c r="E22" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F22" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G22" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>2733</v>
+        <v>2725</v>
       </c>
       <c r="K22" t="s">
-        <v>2734</v>
+        <v>2726</v>
       </c>
       <c r="L22" t="s">
-        <v>2733</v>
+        <v>2725</v>
       </c>
       <c r="M22" t="s">
-        <v>2735</v>
+        <v>2727</v>
       </c>
       <c r="N22" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O22" t="s">
-        <v>2736</v>
+        <v>2728</v>
       </c>
       <c r="P22" t="n">
         <v>172304</v>
@@ -15490,30 +15279,30 @@
         <v>705</v>
       </c>
       <c r="E23" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F23" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G23" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>2737</v>
+        <v>2729</v>
       </c>
       <c r="K23" t="s">
-        <v>2738</v>
+        <v>2730</v>
       </c>
       <c r="L23" t="s">
-        <v>2737</v>
+        <v>2729</v>
       </c>
       <c r="M23" t="s">
-        <v>2739</v>
+        <v>2731</v>
       </c>
       <c r="N23" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O23"/>
       <c r="P23" t="n">
@@ -15534,33 +15323,33 @@
         <v>765</v>
       </c>
       <c r="E24" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F24" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G24" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>2740</v>
+        <v>2732</v>
       </c>
       <c r="K24" t="s">
-        <v>2741</v>
+        <v>2733</v>
       </c>
       <c r="L24" t="s">
-        <v>2740</v>
+        <v>2732</v>
       </c>
       <c r="M24" t="s">
-        <v>2742</v>
+        <v>2734</v>
       </c>
       <c r="N24" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O24" t="s">
-        <v>2743</v>
+        <v>2735</v>
       </c>
       <c r="P24" t="n">
         <v>175630</v>
@@ -15580,33 +15369,33 @@
         <v>597</v>
       </c>
       <c r="E25" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F25" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G25" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>2744</v>
+        <v>2736</v>
       </c>
       <c r="K25" t="s">
-        <v>2745</v>
+        <v>2737</v>
       </c>
       <c r="L25" t="s">
-        <v>2744</v>
+        <v>2736</v>
       </c>
       <c r="M25" t="s">
-        <v>2746</v>
+        <v>2738</v>
       </c>
       <c r="N25" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O25" t="s">
-        <v>2747</v>
+        <v>2739</v>
       </c>
       <c r="P25" t="n">
         <v>178133</v>
@@ -15626,33 +15415,33 @@
         <v>3438</v>
       </c>
       <c r="E26" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F26" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G26" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>2641</v>
+        <v>2633</v>
       </c>
       <c r="K26" t="s">
-        <v>2748</v>
+        <v>2740</v>
       </c>
       <c r="L26" t="s">
-        <v>2641</v>
+        <v>2633</v>
       </c>
       <c r="M26" t="s">
-        <v>2749</v>
+        <v>2741</v>
       </c>
       <c r="N26" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O26" t="s">
-        <v>2643</v>
+        <v>2635</v>
       </c>
       <c r="P26" t="n">
         <v>180560</v>
@@ -15672,33 +15461,33 @@
         <v>1620</v>
       </c>
       <c r="E27" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F27" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G27" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>2750</v>
+        <v>2742</v>
       </c>
       <c r="K27" t="s">
-        <v>2751</v>
+        <v>2743</v>
       </c>
       <c r="L27" t="s">
-        <v>2750</v>
+        <v>2742</v>
       </c>
       <c r="M27" t="s">
-        <v>2752</v>
+        <v>2744</v>
       </c>
       <c r="N27" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O27" t="s">
-        <v>2753</v>
+        <v>2745</v>
       </c>
       <c r="P27" t="n">
         <v>183410</v>
@@ -15718,33 +15507,33 @@
         <v>970</v>
       </c>
       <c r="E28" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F28" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G28" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>2754</v>
+        <v>2746</v>
       </c>
       <c r="K28" t="s">
-        <v>2755</v>
+        <v>2747</v>
       </c>
       <c r="L28" t="s">
-        <v>2754</v>
+        <v>2746</v>
       </c>
       <c r="M28" t="s">
-        <v>2756</v>
+        <v>2748</v>
       </c>
       <c r="N28" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O28" t="s">
-        <v>2757</v>
+        <v>2749</v>
       </c>
       <c r="P28" t="n">
         <v>184216</v>
@@ -15764,33 +15553,33 @@
         <v>2235</v>
       </c>
       <c r="E29" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F29" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G29" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>2758</v>
+        <v>2750</v>
       </c>
       <c r="K29" t="s">
-        <v>2759</v>
+        <v>2751</v>
       </c>
       <c r="L29" t="s">
-        <v>2758</v>
+        <v>2750</v>
       </c>
       <c r="M29" t="s">
-        <v>2760</v>
+        <v>2752</v>
       </c>
       <c r="N29" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O29" t="s">
-        <v>2761</v>
+        <v>2753</v>
       </c>
       <c r="P29" t="n">
         <v>185658</v>
@@ -15810,33 +15599,33 @@
         <v>1035</v>
       </c>
       <c r="E30" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F30" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G30" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>2762</v>
+        <v>2754</v>
       </c>
       <c r="K30" t="s">
-        <v>2763</v>
+        <v>2755</v>
       </c>
       <c r="L30" t="s">
-        <v>2762</v>
+        <v>2754</v>
       </c>
       <c r="M30" t="s">
-        <v>2764</v>
+        <v>2756</v>
       </c>
       <c r="N30" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O30" t="s">
-        <v>2765</v>
+        <v>2757</v>
       </c>
       <c r="P30" t="n">
         <v>188794</v>
@@ -15856,33 +15645,33 @@
         <v>2286</v>
       </c>
       <c r="E31" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F31" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G31" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>2766</v>
+        <v>2758</v>
       </c>
       <c r="K31" t="s">
-        <v>2767</v>
+        <v>2759</v>
       </c>
       <c r="L31" t="s">
-        <v>2766</v>
+        <v>2758</v>
       </c>
       <c r="M31" t="s">
-        <v>2768</v>
+        <v>2760</v>
       </c>
       <c r="N31" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O31" t="s">
-        <v>2769</v>
+        <v>2761</v>
       </c>
       <c r="P31" t="n">
         <v>190646</v>
@@ -15902,33 +15691,33 @@
         <v>666</v>
       </c>
       <c r="E32" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F32" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G32" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>2770</v>
+        <v>2762</v>
       </c>
       <c r="K32" t="s">
-        <v>2771</v>
+        <v>2763</v>
       </c>
       <c r="L32" t="s">
-        <v>2770</v>
+        <v>2762</v>
       </c>
       <c r="M32" t="s">
-        <v>2772</v>
+        <v>2764</v>
       </c>
       <c r="N32" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O32" t="s">
-        <v>2773</v>
+        <v>2765</v>
       </c>
       <c r="P32" t="n">
         <v>192292</v>
@@ -15948,33 +15737,33 @@
         <v>1434</v>
       </c>
       <c r="E33" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F33" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G33" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>2774</v>
+        <v>2766</v>
       </c>
       <c r="K33" t="s">
-        <v>2775</v>
+        <v>2767</v>
       </c>
       <c r="L33" t="s">
-        <v>2774</v>
+        <v>2766</v>
       </c>
       <c r="M33" t="s">
-        <v>2776</v>
+        <v>2768</v>
       </c>
       <c r="N33" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O33" t="s">
-        <v>2777</v>
+        <v>2769</v>
       </c>
       <c r="P33" t="n">
         <v>193514</v>
@@ -15994,33 +15783,33 @@
         <v>267</v>
       </c>
       <c r="E34" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F34" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G34" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>2778</v>
+        <v>2770</v>
       </c>
       <c r="K34" t="s">
-        <v>2779</v>
+        <v>2771</v>
       </c>
       <c r="L34" t="s">
-        <v>2778</v>
+        <v>2770</v>
       </c>
       <c r="M34" t="s">
-        <v>2780</v>
+        <v>2772</v>
       </c>
       <c r="N34" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O34" t="s">
-        <v>2781</v>
+        <v>2773</v>
       </c>
       <c r="P34" t="n">
         <v>194406</v>
@@ -16040,33 +15829,33 @@
         <v>1350</v>
       </c>
       <c r="E35" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F35" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G35" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>2782</v>
+        <v>2774</v>
       </c>
       <c r="K35" t="s">
-        <v>2783</v>
+        <v>2775</v>
       </c>
       <c r="L35" t="s">
-        <v>2782</v>
+        <v>2774</v>
       </c>
       <c r="M35" t="s">
-        <v>2784</v>
+        <v>2776</v>
       </c>
       <c r="N35" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O35" t="s">
-        <v>2785</v>
+        <v>2777</v>
       </c>
       <c r="P35" t="n">
         <v>195842</v>
@@ -16086,33 +15875,33 @@
         <v>1572</v>
       </c>
       <c r="E36" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F36" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G36" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" t="s">
-        <v>2786</v>
+        <v>2778</v>
       </c>
       <c r="K36" t="s">
-        <v>2787</v>
+        <v>2779</v>
       </c>
       <c r="L36" t="s">
-        <v>2786</v>
+        <v>2778</v>
       </c>
       <c r="M36" t="s">
-        <v>2788</v>
+        <v>2780</v>
       </c>
       <c r="N36" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O36" t="s">
-        <v>2789</v>
+        <v>2781</v>
       </c>
       <c r="P36" t="n">
         <v>197734</v>
@@ -16132,33 +15921,33 @@
         <v>2064</v>
       </c>
       <c r="E37" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F37" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G37" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" t="s">
-        <v>2790</v>
+        <v>2782</v>
       </c>
       <c r="K37" t="s">
-        <v>2791</v>
+        <v>2783</v>
       </c>
       <c r="L37" t="s">
-        <v>2790</v>
+        <v>2782</v>
       </c>
       <c r="M37" t="s">
-        <v>2792</v>
+        <v>2784</v>
       </c>
       <c r="N37" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O37" t="s">
-        <v>2793</v>
+        <v>2785</v>
       </c>
       <c r="P37" t="n">
         <v>199844</v>
@@ -16178,33 +15967,33 @@
         <v>861</v>
       </c>
       <c r="E38" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F38" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G38" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" t="s">
-        <v>2636</v>
+        <v>2628</v>
       </c>
       <c r="K38" t="s">
-        <v>2794</v>
+        <v>2786</v>
       </c>
       <c r="L38" t="s">
-        <v>2636</v>
+        <v>2628</v>
       </c>
       <c r="M38" t="s">
-        <v>2795</v>
+        <v>2787</v>
       </c>
       <c r="N38" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O38" t="s">
-        <v>2637</v>
+        <v>2629</v>
       </c>
       <c r="P38" t="n">
         <v>201506</v>
@@ -16224,33 +16013,33 @@
         <v>2772</v>
       </c>
       <c r="E39" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F39" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G39" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" t="s">
-        <v>2796</v>
+        <v>2788</v>
       </c>
       <c r="K39" t="s">
-        <v>2797</v>
+        <v>2789</v>
       </c>
       <c r="L39" t="s">
-        <v>2796</v>
+        <v>2788</v>
       </c>
       <c r="M39" t="s">
-        <v>2798</v>
+        <v>2790</v>
       </c>
       <c r="N39" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O39" t="s">
-        <v>2799</v>
+        <v>2791</v>
       </c>
       <c r="P39" t="n">
         <v>203578</v>
@@ -16270,33 +16059,33 @@
         <v>1584</v>
       </c>
       <c r="E40" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F40" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G40" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" t="s">
-        <v>2800</v>
+        <v>2792</v>
       </c>
       <c r="K40" t="s">
-        <v>2801</v>
+        <v>2793</v>
       </c>
       <c r="L40" t="s">
-        <v>2800</v>
+        <v>2792</v>
       </c>
       <c r="M40" t="s">
-        <v>2802</v>
+        <v>2794</v>
       </c>
       <c r="N40" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O40" t="s">
-        <v>2803</v>
+        <v>2795</v>
       </c>
       <c r="P40" t="n">
         <v>206042</v>
@@ -16316,33 +16105,33 @@
         <v>831</v>
       </c>
       <c r="E41" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F41" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G41" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" t="s">
-        <v>2804</v>
+        <v>2796</v>
       </c>
       <c r="K41" t="s">
-        <v>2805</v>
+        <v>2797</v>
       </c>
       <c r="L41" t="s">
-        <v>2804</v>
+        <v>2796</v>
       </c>
       <c r="M41" t="s">
-        <v>2806</v>
+        <v>2798</v>
       </c>
       <c r="N41" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O41" t="s">
-        <v>2807</v>
+        <v>2799</v>
       </c>
       <c r="P41" t="n">
         <v>208059</v>
@@ -16362,33 +16151,33 @@
         <v>1254</v>
       </c>
       <c r="E42" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F42" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G42" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H42"/>
       <c r="I42"/>
       <c r="J42" t="s">
-        <v>2808</v>
+        <v>2800</v>
       </c>
       <c r="K42" t="s">
-        <v>2809</v>
+        <v>2801</v>
       </c>
       <c r="L42" t="s">
-        <v>2808</v>
+        <v>2800</v>
       </c>
       <c r="M42" t="s">
-        <v>2810</v>
+        <v>2802</v>
       </c>
       <c r="N42" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O42" t="s">
-        <v>2811</v>
+        <v>2803</v>
       </c>
       <c r="P42" t="n">
         <v>209606</v>
@@ -16408,33 +16197,33 @@
         <v>1185</v>
       </c>
       <c r="E43" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F43" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G43" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43" t="s">
-        <v>2812</v>
+        <v>2804</v>
       </c>
       <c r="K43" t="s">
-        <v>2813</v>
+        <v>2805</v>
       </c>
       <c r="L43" t="s">
-        <v>2812</v>
+        <v>2804</v>
       </c>
       <c r="M43" t="s">
-        <v>2814</v>
+        <v>2806</v>
       </c>
       <c r="N43" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O43" t="s">
-        <v>2815</v>
+        <v>2807</v>
       </c>
       <c r="P43" t="n">
         <v>211284</v>
@@ -16454,33 +16243,33 @@
         <v>591</v>
       </c>
       <c r="E44" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F44" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G44" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44" t="s">
-        <v>2816</v>
+        <v>2808</v>
       </c>
       <c r="K44" t="s">
-        <v>2817</v>
+        <v>2809</v>
       </c>
       <c r="L44" t="s">
-        <v>2816</v>
+        <v>2808</v>
       </c>
       <c r="M44" t="s">
-        <v>2818</v>
+        <v>2810</v>
       </c>
       <c r="N44" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O44" t="s">
-        <v>2819</v>
+        <v>2811</v>
       </c>
       <c r="P44" t="n">
         <v>212882</v>
@@ -16500,33 +16289,33 @@
         <v>462</v>
       </c>
       <c r="E45" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F45" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G45" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45" t="s">
-        <v>2820</v>
+        <v>2812</v>
       </c>
       <c r="K45" t="s">
-        <v>2821</v>
+        <v>2813</v>
       </c>
       <c r="L45" t="s">
-        <v>2820</v>
+        <v>2812</v>
       </c>
       <c r="M45" t="s">
-        <v>2822</v>
+        <v>2814</v>
       </c>
       <c r="N45" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O45" t="s">
-        <v>2823</v>
+        <v>2815</v>
       </c>
       <c r="P45" t="n">
         <v>213668</v>
@@ -16546,33 +16335,33 @@
         <v>672</v>
       </c>
       <c r="E46" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F46" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G46" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46" t="s">
-        <v>2824</v>
+        <v>2816</v>
       </c>
       <c r="K46" t="s">
-        <v>2825</v>
+        <v>2817</v>
       </c>
       <c r="L46" t="s">
-        <v>2824</v>
+        <v>2816</v>
       </c>
       <c r="M46" t="s">
-        <v>2826</v>
+        <v>2818</v>
       </c>
       <c r="N46" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O46" t="s">
-        <v>2827</v>
+        <v>2819</v>
       </c>
       <c r="P46" t="n">
         <v>214412</v>
@@ -16592,33 +16381,33 @@
         <v>2631</v>
       </c>
       <c r="E47" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F47" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G47" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H47"/>
       <c r="I47"/>
       <c r="J47" t="s">
-        <v>2828</v>
+        <v>2820</v>
       </c>
       <c r="K47" t="s">
-        <v>2829</v>
+        <v>2821</v>
       </c>
       <c r="L47" t="s">
-        <v>2828</v>
+        <v>2820</v>
       </c>
       <c r="M47" t="s">
-        <v>2830</v>
+        <v>2822</v>
       </c>
       <c r="N47" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O47" t="s">
-        <v>2831</v>
+        <v>2823</v>
       </c>
       <c r="P47" t="n">
         <v>216378</v>
@@ -16638,33 +16427,33 @@
         <v>3231</v>
       </c>
       <c r="E48" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F48" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G48" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H48"/>
       <c r="I48"/>
       <c r="J48" t="s">
-        <v>2832</v>
+        <v>2824</v>
       </c>
       <c r="K48" t="s">
-        <v>2833</v>
+        <v>2825</v>
       </c>
       <c r="L48" t="s">
-        <v>2832</v>
+        <v>2824</v>
       </c>
       <c r="M48" t="s">
-        <v>2701</v>
+        <v>2693</v>
       </c>
       <c r="N48" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O48" t="s">
-        <v>2834</v>
+        <v>2826</v>
       </c>
       <c r="P48" t="n">
         <v>219672</v>
@@ -16684,30 +16473,30 @@
         <v>558</v>
       </c>
       <c r="E49" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F49" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G49" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H49"/>
       <c r="I49"/>
       <c r="J49" t="s">
-        <v>2835</v>
+        <v>2827</v>
       </c>
       <c r="K49" t="s">
-        <v>2836</v>
+        <v>2828</v>
       </c>
       <c r="L49" t="s">
-        <v>2835</v>
+        <v>2827</v>
       </c>
       <c r="M49" t="s">
-        <v>2701</v>
+        <v>2693</v>
       </c>
       <c r="N49" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O49"/>
       <c r="P49" t="n">
@@ -16728,33 +16517,33 @@
         <v>438</v>
       </c>
       <c r="E50" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F50" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G50" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H50"/>
       <c r="I50"/>
       <c r="J50" t="s">
-        <v>2837</v>
+        <v>2829</v>
       </c>
       <c r="K50" t="s">
-        <v>2838</v>
+        <v>2830</v>
       </c>
       <c r="L50" t="s">
-        <v>2837</v>
+        <v>2829</v>
       </c>
       <c r="M50" t="s">
-        <v>2839</v>
+        <v>2831</v>
       </c>
       <c r="N50" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O50" t="s">
-        <v>2840</v>
+        <v>2832</v>
       </c>
       <c r="P50" t="n">
         <v>222858</v>
@@ -16774,33 +16563,33 @@
         <v>1833</v>
       </c>
       <c r="E51" t="s">
-        <v>2675</v>
+        <v>2667</v>
       </c>
       <c r="F51" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="G51" t="s">
-        <v>2667</v>
+        <v>2659</v>
       </c>
       <c r="H51"/>
       <c r="I51"/>
       <c r="J51" t="s">
-        <v>2841</v>
+        <v>2833</v>
       </c>
       <c r="K51" t="s">
-        <v>2842</v>
+        <v>2834</v>
       </c>
       <c r="L51" t="s">
-        <v>2841</v>
+        <v>2833</v>
       </c>
       <c r="M51" t="s">
-        <v>2843</v>
+        <v>2835</v>
       </c>
       <c r="N51" t="s">
-        <v>2673</v>
+        <v>2665</v>
       </c>
       <c r="O51" t="s">
-        <v>2844</v>
+        <v>2836</v>
       </c>
       <c r="P51" t="n">
         <v>224283</v>
@@ -37053,13 +36842,13 @@
         <v>970</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00000433026862522456</v>
+        <v>0.00000590923681702533</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000164550207758533</v>
+        <v>0.000224550999046963</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001002799050052</v>
+        <v>0.000136845484183745</v>
       </c>
       <c r="J2" t="s">
         <v>971</v>
